--- a/Employee_Reports_wi48/Joevergil Cajocson Dormitorio Q0138.xlsx
+++ b/Employee_Reports_wi48/Joevergil Cajocson Dormitorio Q0138.xlsx
@@ -37,7 +37,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -54,12 +54,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FFFACD"/>
         <bgColor rgb="00FFFACD"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
-        <bgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
   </fills>
@@ -81,7 +75,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -93,9 +87,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -463,7 +454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K37"/>
+  <dimension ref="A1:K38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -578,11 +569,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -627,11 +618,11 @@
         </is>
       </c>
       <c r="H4" s="3" t="n">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -676,11 +667,11 @@
         </is>
       </c>
       <c r="H5" s="3" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -725,11 +716,11 @@
         </is>
       </c>
       <c r="H6" s="3" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -774,11 +765,11 @@
         </is>
       </c>
       <c r="H7" s="3" t="n">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -823,11 +814,11 @@
         </is>
       </c>
       <c r="H8" s="4" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J8" s="4" t="inlineStr">
@@ -872,11 +863,11 @@
         </is>
       </c>
       <c r="H9" s="3" t="n">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -887,53 +878,53 @@
       <c r="K9" s="3" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="n">
+      <c r="A10" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>TT+RA (Cargo Trainings)</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>CARGO</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D10" s="4" t="inlineStr">
         <is>
           <t>LSME-CRG-M-007</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="E10" s="4" t="inlineStr">
         <is>
           <t>EQUIPMENT MANUAL</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="F10" s="4" t="inlineStr">
         <is>
           <t>22-Aug-2024</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="G10" s="4" t="inlineStr">
         <is>
           <t>22-Aug-2026</t>
         </is>
       </c>
-      <c r="H10" s="3" t="n">
-        <v>40</v>
-      </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t>12-Jul-2026</t>
-        </is>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="inlineStr"/>
+      <c r="H10" s="4" t="n">
+        <v>37</v>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>15-Jul-2026</t>
+        </is>
+      </c>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>EXPIRING SOON</t>
+        </is>
+      </c>
+      <c r="K10" s="4" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
@@ -970,11 +961,11 @@
         </is>
       </c>
       <c r="H11" s="3" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1019,11 +1010,11 @@
         </is>
       </c>
       <c r="H12" s="3" t="n">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1068,11 +1059,11 @@
         </is>
       </c>
       <c r="H13" s="3" t="n">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1117,11 +1108,11 @@
         </is>
       </c>
       <c r="H14" s="3" t="n">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -1166,11 +1157,11 @@
         </is>
       </c>
       <c r="H15" s="3" t="n">
-        <v>660</v>
+        <v>657</v>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1215,11 +1206,11 @@
         </is>
       </c>
       <c r="H16" s="4" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J16" s="4" t="inlineStr">
@@ -1264,11 +1255,11 @@
         </is>
       </c>
       <c r="H17" s="3" t="n">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -1313,11 +1304,11 @@
         </is>
       </c>
       <c r="H18" s="3" t="n">
-        <v>660</v>
+        <v>657</v>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
@@ -1362,11 +1353,11 @@
         </is>
       </c>
       <c r="H19" s="3" t="n">
-        <v>660</v>
+        <v>657</v>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -1411,11 +1402,11 @@
         </is>
       </c>
       <c r="H20" s="3" t="n">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
@@ -1460,11 +1451,11 @@
         </is>
       </c>
       <c r="H21" s="3" t="n">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
@@ -1510,11 +1501,11 @@
         </is>
       </c>
       <c r="H22" s="3" t="n">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
@@ -1559,11 +1550,11 @@
         </is>
       </c>
       <c r="H23" s="3" t="n">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
@@ -1608,11 +1599,11 @@
         </is>
       </c>
       <c r="H24" s="3" t="n">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
@@ -1645,11 +1636,11 @@
         </is>
       </c>
       <c r="H25" s="3" t="n">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
@@ -1694,11 +1685,11 @@
         </is>
       </c>
       <c r="H26" s="3" t="n">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
@@ -1743,11 +1734,11 @@
         </is>
       </c>
       <c r="H27" s="3" t="n">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
@@ -1758,102 +1749,102 @@
       <c r="K27" s="3" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="n">
+      <c r="A28" s="3" t="n">
         <v>26</v>
       </c>
-      <c r="B28" s="5" t="inlineStr">
+      <c r="B28" s="3" t="inlineStr">
         <is>
           <t>Contigency Plan During Heavy Rainfall (SOPs)</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr">
+      <c r="C28" s="3" t="inlineStr">
         <is>
           <t>IMS</t>
         </is>
       </c>
-      <c r="D28" s="5" t="inlineStr">
+      <c r="D28" s="3" t="inlineStr">
         <is>
           <t>LSME-IMS-SOP-018</t>
         </is>
       </c>
-      <c r="E28" s="5" t="inlineStr">
+      <c r="E28" s="3" t="inlineStr">
         <is>
           <t>SOP</t>
         </is>
       </c>
-      <c r="F28" s="5" t="inlineStr">
-        <is>
-          <t>18-Mar-2025</t>
-        </is>
-      </c>
-      <c r="G28" s="5" t="inlineStr">
-        <is>
-          <t>18-Mar-2026</t>
-        </is>
-      </c>
-      <c r="H28" s="5" t="n">
-        <v>-117</v>
-      </c>
-      <c r="I28" s="5" t="inlineStr">
-        <is>
-          <t>12-Jul-2026</t>
-        </is>
-      </c>
-      <c r="J28" s="5" t="inlineStr">
-        <is>
-          <t>EXPIRED</t>
-        </is>
-      </c>
-      <c r="K28" s="5" t="inlineStr"/>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>21-May-2026</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>21-May-2027</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="n">
+        <v>309</v>
+      </c>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>15-Jul-2026</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="n">
+      <c r="A29" s="3" t="n">
         <v>27</v>
       </c>
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>Replacement Procedure Of ASI Gateway (SOPs)</t>
-        </is>
-      </c>
-      <c r="C29" s="5" t="inlineStr">
-        <is>
-          <t>CARGO</t>
-        </is>
-      </c>
-      <c r="D29" s="5" t="inlineStr">
-        <is>
-          <t>LSME-CRG-SOP-041</t>
-        </is>
-      </c>
-      <c r="E29" s="5" t="inlineStr">
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>Procedure For Handling New or Unfamilliar Task (SOPs)</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>IMS</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>LSME-IMS-SOP-022</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
         <is>
           <t>SOP</t>
         </is>
       </c>
-      <c r="F29" s="5" t="inlineStr">
-        <is>
-          <t>04-Apr-2025</t>
-        </is>
-      </c>
-      <c r="G29" s="5" t="inlineStr">
-        <is>
-          <t>04-Apr-2026</t>
-        </is>
-      </c>
-      <c r="H29" s="5" t="n">
-        <v>-100</v>
-      </c>
-      <c r="I29" s="5" t="inlineStr">
-        <is>
-          <t>12-Jul-2026</t>
-        </is>
-      </c>
-      <c r="J29" s="5" t="inlineStr">
-        <is>
-          <t>EXPIRED</t>
-        </is>
-      </c>
-      <c r="K29" s="5" t="inlineStr"/>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>21-May-2026</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>21-May-2027</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="n">
+        <v>309</v>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>15-Jul-2026</t>
+        </is>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="3" t="n">
@@ -1861,7 +1852,7 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Replacing Bearings Of ULD Hoist Counterweight Pulley (SOPs)</t>
+          <t>Replacement Procedure Of ASI Gateway (SOPs)</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
@@ -1871,7 +1862,7 @@
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>LSME-CRG-SOP-011</t>
+          <t>LSME-CRG-SOP-041</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
@@ -1881,20 +1872,20 @@
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>31-Aug-2025</t>
+          <t>10-Apr-2026</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>31-Aug-2026</t>
+          <t>10-Apr-2027</t>
         </is>
       </c>
       <c r="H30" s="3" t="n">
-        <v>49</v>
+        <v>268</v>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
@@ -1910,7 +1901,7 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Overload and Load Testing Procedure In ULD Hoist (SOPs)</t>
+          <t>Replacing Bearings Of ULD Hoist Counterweight Pulley (SOPs)</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
@@ -1920,7 +1911,7 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>LSME-CRG-SOP-018</t>
+          <t>LSME-CRG-SOP-011</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
@@ -1939,11 +1930,11 @@
         </is>
       </c>
       <c r="H31" s="3" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
@@ -1959,28 +1950,40 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>ULD Hoist Drve Motor Replacement (SOPs)</t>
-        </is>
-      </c>
-      <c r="C32" s="3" t="inlineStr"/>
-      <c r="D32" s="3" t="inlineStr"/>
-      <c r="E32" s="3" t="inlineStr"/>
+          <t>Overload and Load Testing Procedure In ULD Hoist (SOPs)</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>CARGO</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>LSME-CRG-SOP-018</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>SOP</t>
+        </is>
+      </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>24-Nov-2025</t>
+          <t>31-Aug-2025</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>24-Nov-2026</t>
+          <t>31-Aug-2026</t>
         </is>
       </c>
       <c r="H32" s="3" t="n">
-        <v>134</v>
+        <v>46</v>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
@@ -1996,7 +1999,7 @@
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>EOP For ULD System Failure (SOPs)</t>
+          <t>ULD Hoist Drve Motor Replacement (SOPs)</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr"/>
@@ -2004,20 +2007,20 @@
       <c r="E33" s="3" t="inlineStr"/>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>15-Jun-2026</t>
+          <t>24-Nov-2025</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>15-Jun-2027</t>
+          <t>24-Nov-2026</t>
         </is>
       </c>
       <c r="H33" s="3" t="n">
-        <v>337</v>
+        <v>131</v>
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
@@ -2033,7 +2036,7 @@
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>EOP For CS System Failure (SOPs)</t>
+          <t>EOP For ULD System Failure (SOPs)</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr"/>
@@ -2050,11 +2053,11 @@
         </is>
       </c>
       <c r="H34" s="3" t="n">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
@@ -2070,7 +2073,7 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>EOP For Cold Storage System due to Equipment Failure (SOPs)</t>
+          <t>EOP For CS System Failure (SOPs)</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr"/>
@@ -2087,11 +2090,11 @@
         </is>
       </c>
       <c r="H35" s="3" t="n">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
@@ -2107,7 +2110,7 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>IS0 55001 (Other Trainings)</t>
+          <t>EOP For Cold Storage System due to Equipment Failure (SOPs)</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr"/>
@@ -2115,20 +2118,20 @@
       <c r="E36" s="3" t="inlineStr"/>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>01-Jul-2025</t>
+          <t>15-Jun-2026</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>01-Jul-2027</t>
+          <t>15-Jun-2027</t>
         </is>
       </c>
       <c r="H36" s="3" t="n">
-        <v>353</v>
+        <v>334</v>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
@@ -2139,25 +2142,62 @@
       <c r="K36" s="3" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="inlineStr"/>
+      <c r="A37" s="3" t="n">
+        <v>35</v>
+      </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>YOU ARE LISTED AS ; SENIOR TECHNICIAN</t>
-        </is>
-      </c>
-      <c r="C37" s="3" t="inlineStr">
-        <is>
-          <t>&amp; THIS IS YOUR TRAINING DASHBOARD</t>
-        </is>
-      </c>
+          <t>IS0 55001 (Other Trainings)</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr"/>
       <c r="D37" s="3" t="inlineStr"/>
       <c r="E37" s="3" t="inlineStr"/>
-      <c r="F37" s="3" t="inlineStr"/>
-      <c r="G37" s="3" t="inlineStr"/>
-      <c r="H37" s="3" t="inlineStr"/>
-      <c r="I37" s="3" t="inlineStr"/>
-      <c r="J37" s="3" t="inlineStr"/>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>01-Jul-2025</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="inlineStr">
+        <is>
+          <t>01-Jul-2027</t>
+        </is>
+      </c>
+      <c r="H37" s="3" t="n">
+        <v>350</v>
+      </c>
+      <c r="I37" s="3" t="inlineStr">
+        <is>
+          <t>15-Jul-2026</t>
+        </is>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
       <c r="K37" s="3" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr"/>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>YOU ARE LISTED AS ; SENIOR TECHNICIAN</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>&amp; THIS IS YOUR TRAINING DASHBOARD</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr"/>
+      <c r="E38" s="3" t="inlineStr"/>
+      <c r="F38" s="3" t="inlineStr"/>
+      <c r="G38" s="3" t="inlineStr"/>
+      <c r="H38" s="3" t="inlineStr"/>
+      <c r="I38" s="3" t="inlineStr"/>
+      <c r="J38" s="3" t="inlineStr"/>
+      <c r="K38" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2311,7 +2351,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7949</v>
+        <v>7946</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -2340,7 +2380,7 @@
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>7964</v>
+        <v>7961</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
@@ -2369,7 +2409,7 @@
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>7964</v>
+        <v>7961</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
@@ -2392,7 +2432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -2450,21 +2490,21 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>ews 20ft</t>
+          <t>stacker crane</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>25-May-2026</t>
+          <t>09-Jul-2026</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>19-Apr-2048</t>
+          <t>03-Jun-2048</t>
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7951</v>
+        <v>7993</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -2479,21 +2519,21 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>ews 10 ft</t>
+          <t>h9tv</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>25-May-2026</t>
+          <t>09-Jul-2026</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>19-Apr-2048</t>
+          <t>03-Jun-2048</t>
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>7951</v>
+        <v>7993</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
@@ -2508,21 +2548,21 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>uld hoist</t>
+          <t>ews 20ft</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>31-May-2026</t>
+          <t>25-May-2026</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>25-Apr-2048</t>
+          <t>19-Apr-2048</t>
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>7957</v>
+        <v>7948</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
@@ -2537,21 +2577,21 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>truckdock 15ft</t>
+          <t>ews 10 ft</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>30-May-2026</t>
+          <t>25-May-2026</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>24-Apr-2048</t>
+          <t>19-Apr-2048</t>
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>7956</v>
+        <v>7948</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -2566,21 +2606,21 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>truckdock  20ft</t>
+          <t>uld hoist</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>29-May-2026</t>
+          <t>31-May-2026</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>23-Apr-2048</t>
+          <t>25-Apr-2048</t>
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>7955</v>
+        <v>7954</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
@@ -2595,7 +2635,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>turntable</t>
+          <t>truckdock 15ft</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
@@ -2609,7 +2649,7 @@
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>7956</v>
+        <v>7953</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -2624,21 +2664,21 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>tilting deck</t>
+          <t>truckdock  20ft</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>31-May-2026</t>
+          <t>29-May-2026</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>25-Apr-2048</t>
+          <t>23-Apr-2048</t>
         </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>7957</v>
+        <v>7952</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
@@ -2653,21 +2693,21 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>uldtv 20ft</t>
+          <t>turntable</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>01-Jun-2026</t>
+          <t>30-May-2026</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>26-Apr-2048</t>
+          <t>24-Apr-2048</t>
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>7958</v>
+        <v>7953</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
@@ -2682,21 +2722,21 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>uldtv 15ft</t>
+          <t>tilting deck</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>01-Jun-2026</t>
+          <t>31-May-2026</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>26-Apr-2048</t>
+          <t>25-Apr-2048</t>
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>7958</v>
+        <v>7954</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
@@ -2711,21 +2751,21 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>bbtv 20ft</t>
+          <t>uldtv 20ft</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>12-Jun-2026</t>
+          <t>01-Jun-2026</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>07-May-2048</t>
+          <t>26-Apr-2048</t>
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>7969</v>
+        <v>7955</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
@@ -2740,21 +2780,21 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>bbtv 15ft</t>
+          <t>uldtv 15ft</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>12-Jun-2026</t>
+          <t>01-Jun-2026</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>07-May-2048</t>
+          <t>26-Apr-2048</t>
         </is>
       </c>
       <c r="E13" s="3" t="n">
-        <v>7969</v>
+        <v>7955</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -2769,21 +2809,21 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>fmc deck</t>
+          <t>bbtv 20ft</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>24-May-2026</t>
+          <t>12-Jun-2026</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>18-Apr-2048</t>
+          <t>07-May-2048</t>
         </is>
       </c>
       <c r="E14" s="3" t="n">
-        <v>7950</v>
+        <v>7966</v>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
@@ -2798,21 +2838,21 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>powered roller deckmatarsop</t>
+          <t>bbtv 15ft</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>26-May-2026</t>
+          <t>12-Jun-2026</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>20-Apr-2048</t>
+          <t>07-May-2048</t>
         </is>
       </c>
       <c r="E15" s="3" t="n">
-        <v>7952</v>
+        <v>7966</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
@@ -2827,21 +2867,21 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>non powered roller deckmatarsop</t>
+          <t>fmc deck</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>29-May-2026</t>
+          <t>24-May-2026</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>23-Apr-2048</t>
+          <t>18-Apr-2048</t>
         </is>
       </c>
       <c r="E16" s="3" t="n">
-        <v>7955</v>
+        <v>7947</v>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
@@ -2856,21 +2896,21 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>ball deck</t>
+          <t>powered roller deckmatarsop</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>24-May-2026</t>
+          <t>26-May-2026</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>18-Apr-2048</t>
+          <t>20-Apr-2048</t>
         </is>
       </c>
       <c r="E17" s="3" t="n">
-        <v>7950</v>
+        <v>7949</v>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
@@ -2885,17 +2925,17 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>floor scale</t>
+          <t>non powered roller deckmatarsop</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>26-May-2026</t>
+          <t>29-May-2026</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>20-Apr-2048</t>
+          <t>23-Apr-2048</t>
         </is>
       </c>
       <c r="E18" s="3" t="n">
@@ -2907,6 +2947,64 @@
         </is>
       </c>
       <c r="G18" s="3" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>ball deck</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>24-May-2026</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>18-Apr-2048</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>7947</v>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>floor scale</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>26-May-2026</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>20-Apr-2048</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>7949</v>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
